--- a/templates-source/discovery-setup/open-questions-log.xlsx
+++ b/templates-source/discovery-setup/open-questions-log.xlsx
@@ -430,7 +430,7 @@
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="30" customWidth="1" min="9" max="9"/>
@@ -486,7 +486,7 @@
   </sheetData>
   <dataValidations count="2">
     <dataValidation sqref="F2:F1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"High,Medium,Low"</formula1>
+      <formula1>"P1 Goals &amp; scope,P2 Users &amp; processes,P3 Functional,P4 Non-functional"</formula1>
     </dataValidation>
     <dataValidation sqref="G2:G1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Open,Answered,Closed"</formula1>
